--- a/data/trans_dic/IP19C03-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C03-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por empastes</t>
+          <t>Menores que en su última visita al dentista fue por empastes (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,36; 25,62</t>
+          <t>9,31; 25,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,32; 19,97</t>
+          <t>4,57; 19,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 17,99</t>
+          <t>2,95; 19,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,5; 15,56</t>
+          <t>4,4; 15,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,55; 24,64</t>
+          <t>8,34; 25,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,04; 21,31</t>
+          <t>4,85; 22,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,04; 31,17</t>
+          <t>12,03; 31,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 15,48</t>
+          <t>4,4; 15,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,51; 22,01</t>
+          <t>10,78; 22,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 16,77</t>
+          <t>6,24; 17,35</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,66; 22,7</t>
+          <t>9,69; 22,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,52; 13,11</t>
+          <t>5,5; 13,6</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,91; 21,96</t>
+          <t>5,17; 22,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,34; 33,01</t>
+          <t>13,22; 33,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,65; 29,07</t>
+          <t>11,9; 29,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,11; 22,73</t>
+          <t>7,07; 21,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,15; 33,99</t>
+          <t>11,01; 33,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,27; 25,45</t>
+          <t>8,38; 24,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,29; 22,83</t>
+          <t>6,74; 23,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,81; 23,41</t>
+          <t>8,67; 24,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,62; 22,68</t>
+          <t>9,63; 23,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,4; 24,53</t>
+          <t>12,61; 25,39</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,31; 22,93</t>
+          <t>11,32; 23,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,96; 20,42</t>
+          <t>9,88; 20,51</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,22; 33,35</t>
+          <t>11,77; 34,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,36; 33,98</t>
+          <t>13,76; 35,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 17,36</t>
+          <t>0,0; 17,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,61; 37,96</t>
+          <t>12,27; 39,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,42; 25,92</t>
+          <t>10,39; 27,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,89; 35,94</t>
+          <t>14,86; 37,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,36; 22,73</t>
+          <t>4,49; 24,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,75; 21,58</t>
+          <t>3,64; 20,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,65; 25,87</t>
+          <t>11,71; 25,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,37; 31,93</t>
+          <t>16,06; 31,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,38; 16,43</t>
+          <t>4,24; 16,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,28; 24,86</t>
+          <t>8,51; 25,57</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,08; 25,87</t>
+          <t>13,74; 26,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,64; 32,39</t>
+          <t>17,86; 32,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,02; 22,88</t>
+          <t>11,64; 23,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,37; 28,27</t>
+          <t>15,39; 28,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,22; 24,51</t>
+          <t>12,12; 24,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,36; 27,43</t>
+          <t>14,27; 27,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,2; 25,49</t>
+          <t>13,11; 25,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,41; 35,32</t>
+          <t>18,77; 34,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,0; 23,12</t>
+          <t>14,31; 23,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,69; 27,33</t>
+          <t>17,83; 27,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,81; 22,74</t>
+          <t>13,57; 22,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,49; 29,98</t>
+          <t>19,34; 29,61</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,61; 40,08</t>
+          <t>20,06; 40,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,23; 31,42</t>
+          <t>17,34; 31,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,05; 34,09</t>
+          <t>18,06; 35,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,57; 35,9</t>
+          <t>15,68; 38,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,65; 29,66</t>
+          <t>13,13; 28,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,12; 35,7</t>
+          <t>18,85; 35,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,05; 30,61</t>
+          <t>14,6; 29,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,53; 23,12</t>
+          <t>8,23; 23,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,99; 31,14</t>
+          <t>18,34; 30,77</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,27; 31,47</t>
+          <t>19,8; 31,24</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,25; 29,76</t>
+          <t>18,05; 29,34</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,76; 25,85</t>
+          <t>12,55; 26,78</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,25; 39,53</t>
+          <t>15,72; 38,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,96; 31,17</t>
+          <t>6,89; 28,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,91; 38,7</t>
+          <t>12,97; 36,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,93; 24,6</t>
+          <t>8,04; 25,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,86; 18,08</t>
+          <t>1,87; 18,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,81; 28,75</t>
+          <t>9,27; 30,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,07; 36,07</t>
+          <t>11,47; 36,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,87; 20,91</t>
+          <t>2,17; 22,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,35; 25,97</t>
+          <t>11,28; 25,12</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,02; 25,23</t>
+          <t>10,51; 25,46</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15,66; 32,92</t>
+          <t>15,81; 34,26</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,49; 19,61</t>
+          <t>6,78; 19,26</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,21; 24,79</t>
+          <t>17,18; 24,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,48; 25,06</t>
+          <t>17,03; 24,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,54; 21,56</t>
+          <t>14,56; 21,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,36; 21,37</t>
+          <t>14,37; 21,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,94; 20,79</t>
+          <t>13,89; 20,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,59; 23,8</t>
+          <t>16,65; 23,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,25; 22,21</t>
+          <t>15,03; 21,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,88; 19,39</t>
+          <t>12,88; 19,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,25; 21,41</t>
+          <t>16,27; 20,96</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,69; 22,83</t>
+          <t>18,02; 22,96</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,68; 20,41</t>
+          <t>15,64; 20,49</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,65; 19,42</t>
+          <t>14,29; 19,12</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por empastes (tasa de respuesta: 99,49%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>8732</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4778</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3651</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6415</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7474</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4744</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>10506</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>8503</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>16206</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>9522</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>14157</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>14917</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>5103; 13898</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2204; 9508</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1269; 8544</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3161; 11254</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4117; 12724</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1985; 9163</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6076; 15792</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>4226; 14670</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>11224; 23067</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>5559; 15462</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>9063; 20735</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>9228; 22834</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4695</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10419</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10726</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8408</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>7428</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>8037</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7229</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>10874</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>12123</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>18456</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>17954</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>19282</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2094; 8943</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6280; 16047</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>6633; 16375</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4434; 13685</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4080; 12314</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>4449; 12912</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3642; 12700</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>6204; 17397</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>7470; 18090</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>12677; 25530</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>12422; 25374</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>13262; 27545</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>7165</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9258</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1958</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6249</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9194</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>9719</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4143</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3648</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>16360</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>18977</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>6101</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>9897</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4121; 11963</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5741; 14928</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5427</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3426; 10976</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5545; 14648</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5912; 14756</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1542; 8540</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1320; 7511</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>10353; 22969</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>13092; 25601</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2774; 10501</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5460; 16411</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>18585</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>22357</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18826</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>23644</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>17067</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>19781</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>19636</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>33983</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>35652</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>42138</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>38462</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>57627</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>13479; 25549</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>16291; 29223</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>12928; 26260</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>17093; 32142</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>11650; 23703</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>14059; 26948</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>13712; 27086</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>23910; 44496</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>27806; 45777</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>33835; 51774</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>29266; 48159</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>46125; 70606</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>16262</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>19295</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>17508</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>16413</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>14399</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>19509</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>15984</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>15125</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>30661</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>38804</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>33492</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>31538</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>10962; 22138</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>14145; 26096</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>12488; 24443</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>10739; 26278</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>9196; 19840</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>13885; 26085</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10742; 22062</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>8489; 24051</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>22867; 38365</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>30742; 48505</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>25759; 41879</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>21553; 45974</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>10661</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3930</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7714</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6600</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2625</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>6819</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>7332</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>3992</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>13286</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>10748</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>15046</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>10592</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>6287; 15589</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>1769; 7376</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>4228; 11995</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>3607; 11521</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>669; 6553</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>3480; 11394</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>3693; 11906</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>959; 9994</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>8540; 19023</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>6644; 16092</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>10245; 22199</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>6031; 17144</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>66100</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>70037</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>60383</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>67729</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>58188</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>68610</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>76125</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>124288</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>138647</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>125212</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>143853</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>55508; 78021</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>57214; 82578</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>49890; 73547</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>55599; 82636</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>47471; 70306</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>57184; 82313</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>52487; 76230</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>61648; 92173</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>108134; 139324</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>122420; 155987</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>108221; 141763</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>123657; 165513</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C03-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C03-Clase-trans_dic.xlsx
@@ -717,37 +717,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,31; 25,36</t>
+          <t>9,45; 24,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,57; 19,71</t>
+          <t>3,77; 18,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 19,86</t>
+          <t>3,1; 19,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 15,68</t>
+          <t>4,49; 16,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,34; 25,78</t>
+          <t>8,2; 24,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,85; 22,41</t>
+          <t>4,91; 21,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,03; 31,26</t>
+          <t>12,54; 30,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,78; 22,15</t>
+          <t>10,42; 21,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,24; 17,35</t>
+          <t>6,01; 16,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,69; 22,17</t>
+          <t>9,04; 21,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,5; 13,6</t>
+          <t>5,65; 13,65</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,17; 22,08</t>
+          <t>5,17; 22,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,22; 33,79</t>
+          <t>13,41; 33,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,9; 29,38</t>
+          <t>11,48; 28,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,07; 21,83</t>
+          <t>7,05; 22,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,01; 33,24</t>
+          <t>10,59; 33,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,38; 24,33</t>
+          <t>8,15; 23,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,74; 23,51</t>
+          <t>6,57; 23,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,67; 24,3</t>
+          <t>8,78; 24,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,63; 23,33</t>
+          <t>9,89; 22,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,61; 25,39</t>
+          <t>12,46; 25,04</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,32; 23,12</t>
+          <t>11,29; 22,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,88; 20,51</t>
+          <t>9,69; 20,01</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,77; 34,17</t>
+          <t>11,16; 32,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,76; 35,78</t>
+          <t>12,98; 34,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,44</t>
+          <t>1,94; 16,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,27; 39,3</t>
+          <t>11,58; 39,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,39; 27,45</t>
+          <t>10,45; 27,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,86; 37,08</t>
+          <t>15,38; 37,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,49; 24,9</t>
+          <t>4,63; 23,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,64; 20,71</t>
+          <t>3,69; 19,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,71; 25,99</t>
+          <t>12,62; 25,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,06; 31,41</t>
+          <t>16,78; 30,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,24; 16,05</t>
+          <t>4,87; 16,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,51; 25,57</t>
+          <t>8,94; 23,61</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,74; 26,03</t>
+          <t>13,11; 26,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,86; 32,03</t>
+          <t>17,57; 32,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,64; 23,64</t>
+          <t>11,6; 23,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,39; 28,94</t>
+          <t>15,53; 28,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,12; 24,65</t>
+          <t>11,71; 24,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,27; 27,35</t>
+          <t>14,69; 27,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,11; 25,89</t>
+          <t>13,27; 26,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,77; 34,93</t>
+          <t>19,79; 34,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,31; 23,56</t>
+          <t>13,77; 22,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,83; 27,28</t>
+          <t>17,79; 27,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,57; 22,33</t>
+          <t>13,97; 22,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,34; 29,61</t>
+          <t>19,26; 29,68</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,06; 40,5</t>
+          <t>20,36; 40,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,34; 31,98</t>
+          <t>16,56; 31,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,06; 35,34</t>
+          <t>17,82; 34,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15,68; 38,36</t>
+          <t>14,83; 37,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,13; 28,33</t>
+          <t>13,55; 29,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,85; 35,41</t>
+          <t>18,85; 36,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,6; 29,98</t>
+          <t>14,9; 30,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,23; 23,31</t>
+          <t>8,64; 23,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,34; 30,77</t>
+          <t>18,29; 30,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,8; 31,24</t>
+          <t>19,8; 31,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,05; 29,34</t>
+          <t>17,95; 29,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,55; 26,78</t>
+          <t>12,21; 26,04</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,72; 38,97</t>
+          <t>17,08; 38,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,89; 28,71</t>
+          <t>5,33; 28,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,97; 36,79</t>
+          <t>13,8; 39,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,04; 25,68</t>
+          <t>8,09; 25,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,87; 18,34</t>
+          <t>1,84; 16,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,27; 30,37</t>
+          <t>9,56; 30,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,47; 36,99</t>
+          <t>12,47; 36,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,17; 22,64</t>
+          <t>2,93; 22,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,28; 25,12</t>
+          <t>11,08; 24,51</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,51; 25,46</t>
+          <t>9,99; 24,75</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15,81; 34,26</t>
+          <t>14,98; 33,23</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,78; 19,26</t>
+          <t>7,26; 20,68</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,18; 24,15</t>
+          <t>17,07; 24,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,03; 24,58</t>
+          <t>17,26; 24,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,56; 21,46</t>
+          <t>14,47; 21,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,37; 21,36</t>
+          <t>14,29; 21,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,89; 20,58</t>
+          <t>13,73; 20,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,65; 23,97</t>
+          <t>16,7; 23,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,03; 21,83</t>
+          <t>14,89; 22,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,88; 19,26</t>
+          <t>12,91; 19,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,27; 20,96</t>
+          <t>16,5; 21,27</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,02; 22,96</t>
+          <t>17,87; 22,91</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,64; 20,49</t>
+          <t>15,71; 20,56</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,29; 19,12</t>
+          <t>14,43; 19,27</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5103; 13898</t>
+          <t>5180; 13533</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2204; 9508</t>
+          <t>1816; 9080</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1269; 8544</t>
+          <t>1335; 8363</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3161; 11254</t>
+          <t>3219; 12126</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4117; 12724</t>
+          <t>4047; 12255</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1985; 9163</t>
+          <t>2009; 8844</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6076; 15792</t>
+          <t>6337; 15483</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4226; 14670</t>
+          <t>4223; 14672</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11224; 23067</t>
+          <t>10857; 22398</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5559; 15462</t>
+          <t>5360; 15093</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9063; 20735</t>
+          <t>8454; 19918</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9228; 22834</t>
+          <t>9479; 22911</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2094; 8943</t>
+          <t>2095; 9192</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6280; 16047</t>
+          <t>6367; 15948</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6633; 16375</t>
+          <t>6400; 16090</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4434; 13685</t>
+          <t>4420; 14124</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4080; 12314</t>
+          <t>3922; 12339</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4449; 12912</t>
+          <t>4325; 12678</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3642; 12700</t>
+          <t>3550; 12730</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6204; 17397</t>
+          <t>6287; 17874</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7470; 18090</t>
+          <t>7668; 17712</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12677; 25530</t>
+          <t>12529; 25182</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12422; 25374</t>
+          <t>12392; 24308</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13262; 27545</t>
+          <t>13019; 26867</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4121; 11963</t>
+          <t>3908; 11302</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5741; 14928</t>
+          <t>5418; 14588</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5427</t>
+          <t>604; 5176</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3426; 10976</t>
+          <t>3234; 11074</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5545; 14648</t>
+          <t>5577; 14416</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5912; 14756</t>
+          <t>6122; 14979</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1542; 8540</t>
+          <t>1589; 7982</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1320; 7511</t>
+          <t>1340; 7193</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10353; 22969</t>
+          <t>11155; 22486</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13092; 25601</t>
+          <t>13679; 25033</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2774; 10501</t>
+          <t>3186; 10791</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5460; 16411</t>
+          <t>5739; 15153</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13479; 25549</t>
+          <t>12865; 25544</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16291; 29223</t>
+          <t>16030; 29669</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12928; 26260</t>
+          <t>12884; 26568</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17093; 32142</t>
+          <t>17244; 32130</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11650; 23703</t>
+          <t>11259; 23207</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14059; 26948</t>
+          <t>14477; 27399</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13712; 27086</t>
+          <t>13880; 27687</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23910; 44496</t>
+          <t>25206; 43976</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27806; 45777</t>
+          <t>26752; 44613</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33835; 51774</t>
+          <t>33750; 52652</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29266; 48159</t>
+          <t>30137; 48335</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>46125; 70606</t>
+          <t>45916; 70768</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10962; 22138</t>
+          <t>11130; 22035</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14145; 26096</t>
+          <t>13513; 25649</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12488; 24443</t>
+          <t>12323; 23671</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10739; 26278</t>
+          <t>10160; 25883</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9196; 19840</t>
+          <t>9486; 20506</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13885; 26085</t>
+          <t>13886; 26778</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10742; 22062</t>
+          <t>10965; 22426</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8489; 24051</t>
+          <t>8913; 24444</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22867; 38365</t>
+          <t>22807; 38183</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30742; 48505</t>
+          <t>30740; 49204</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25759; 41879</t>
+          <t>25628; 41810</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21553; 45974</t>
+          <t>20962; 44718</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6287; 15589</t>
+          <t>6832; 15553</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1769; 7376</t>
+          <t>1369; 7409</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4228; 11995</t>
+          <t>4499; 12730</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3607; 11521</t>
+          <t>3629; 11659</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>669; 6553</t>
+          <t>659; 5953</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3480; 11394</t>
+          <t>3588; 11462</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3693; 11906</t>
+          <t>4014; 11878</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>959; 9994</t>
+          <t>1291; 9854</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8540; 19023</t>
+          <t>8394; 18561</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6644; 16092</t>
+          <t>6315; 15643</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10245; 22199</t>
+          <t>9707; 21527</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6031; 17144</t>
+          <t>6461; 18402</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>55508; 78021</t>
+          <t>55151; 79388</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>57214; 82578</t>
+          <t>57972; 82771</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>49890; 73547</t>
+          <t>49603; 72667</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>55599; 82636</t>
+          <t>55259; 82782</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>47471; 70306</t>
+          <t>46922; 69388</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>57184; 82313</t>
+          <t>57373; 81694</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>52487; 76230</t>
+          <t>52010; 77573</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>61648; 92173</t>
+          <t>61784; 92942</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>108134; 139324</t>
+          <t>109721; 141389</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>122420; 155987</t>
+          <t>121408; 155692</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>108221; 141763</t>
+          <t>108738; 142245</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>123657; 165513</t>
+          <t>124867; 166820</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C03-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C03-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,62 +649,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15,14%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11,6%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20,8%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8,71%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>15,94%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>9,9%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8,49%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8,94%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>9,07%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>15,56%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10,68%</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>15,14%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,6%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8,85%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>15,56%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>10,68%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>15,14%</t>
-        </is>
-      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,45; 24,7</t>
+          <t>7,55; 24,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 18,82</t>
+          <t>5,04; 21,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,1; 19,44</t>
+          <t>13,04; 31,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 16,89</t>
+          <t>4,43; 15,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,2; 24,83</t>
+          <t>9,36; 25,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,91; 21,63</t>
+          <t>4,32; 19,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,54; 30,65</t>
+          <t>3,21; 17,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 15,27</t>
+          <t>4,47; 15,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,42; 21,51</t>
+          <t>10,51; 22,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,01; 16,94</t>
+          <t>6,04; 16,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,04; 21,3</t>
+          <t>9,66; 22,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,65; 13,65</t>
+          <t>5,34; 12,96</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20,05%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15,14%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13,38%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>14,71%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>11,59%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>21,94%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>19,24%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13,41%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>20,05%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>15,14%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,38%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,17; 22,7</t>
+          <t>11,15; 33,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,41; 33,58</t>
+          <t>8,27; 25,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,48; 28,87</t>
+          <t>7,29; 22,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,05; 22,53</t>
+          <t>8,46; 22,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,59; 33,31</t>
+          <t>4,91; 21,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,15; 23,89</t>
+          <t>13,34; 33,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,57; 23,56</t>
+          <t>11,65; 29,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,78; 24,97</t>
+          <t>7,09; 22,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,89; 22,84</t>
+          <t>9,62; 22,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,46; 25,04</t>
+          <t>12,4; 24,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,29; 22,15</t>
+          <t>11,31; 22,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,69; 20,01</t>
+          <t>9,78; 19,88</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17,23%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24,43%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12,08%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9,98%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>20,47%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>22,19%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6,29%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22,38%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>17,23%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>24,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>12,08%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,16; 32,28</t>
+          <t>9,42; 25,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,98; 34,96</t>
+          <t>14,89; 35,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 16,63</t>
+          <t>4,36; 22,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,58; 39,65</t>
+          <t>3,8; 22,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,45; 27,01</t>
+          <t>11,22; 33,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,38; 37,64</t>
+          <t>12,36; 33,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 23,27</t>
+          <t>1,92; 17,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 19,84</t>
+          <t>10,65; 36,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,62; 25,44</t>
+          <t>12,65; 25,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,78; 30,71</t>
+          <t>16,37; 31,93</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 16,49</t>
+          <t>4,38; 16,43</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,94; 23,61</t>
+          <t>9,03; 24,49</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17,75%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20,07%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18,77%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>25,44%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>18,94%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>24,51%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>16,95%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>21,29%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17,75%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20,07%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,77%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,11; 26,03</t>
+          <t>12,22; 24,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,57; 32,52</t>
+          <t>14,36; 27,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,6; 23,91</t>
+          <t>12,2; 25,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,53; 28,93</t>
+          <t>18,52; 34,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,71; 24,13</t>
+          <t>13,08; 25,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,69; 27,81</t>
+          <t>17,64; 32,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,27; 26,47</t>
+          <t>12,02; 22,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,79; 34,52</t>
+          <t>15,82; 29,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,77; 22,96</t>
+          <t>14,0; 23,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,79; 27,75</t>
+          <t>17,69; 27,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,97; 22,41</t>
+          <t>13,81; 22,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,26; 29,68</t>
+          <t>19,4; 29,23</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>20,56%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>26,48%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21,72%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>14,47%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>29,75%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>23,65%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>25,31%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>23,96%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>20,56%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>26,48%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>21,72%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,36; 40,31</t>
+          <t>13,65; 29,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,56; 31,44</t>
+          <t>18,12; 35,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,82; 34,23</t>
+          <t>14,05; 30,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,83; 37,79</t>
+          <t>7,76; 22,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,55; 29,28</t>
+          <t>20,61; 40,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,85; 36,35</t>
+          <t>16,23; 31,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,9; 30,48</t>
+          <t>17,05; 34,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,64; 23,69</t>
+          <t>12,28; 28,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,29; 30,62</t>
+          <t>18,99; 31,14</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,8; 31,69</t>
+          <t>19,27; 31,47</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,95; 29,29</t>
+          <t>18,25; 29,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,21; 26,04</t>
+          <t>11,76; 22,7</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7,35%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18,17%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>22,78%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8,87%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>26,65%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>15,3%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>23,66%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>14,71%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7,35%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>18,17%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>22,78%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,08; 38,88</t>
+          <t>1,86; 18,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,33; 28,84</t>
+          <t>9,81; 28,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,8; 39,05</t>
+          <t>12,07; 36,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,09; 25,99</t>
+          <t>1,61; 20,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 16,66</t>
+          <t>17,25; 39,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,56; 30,55</t>
+          <t>6,96; 31,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,47; 36,9</t>
+          <t>12,91; 38,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,93; 22,33</t>
+          <t>7,68; 23,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,08; 24,51</t>
+          <t>11,35; 25,97</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,99; 24,75</t>
+          <t>10,02; 25,23</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,98; 33,23</t>
+          <t>15,66; 32,92</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,26; 20,68</t>
+          <t>6,53; 19,54</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>17,03%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19,98%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18,56%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>15,43%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>20,46%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>20,85%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>17,62%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>17,51%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>17,03%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>19,98%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>18,56%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,11%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,07; 24,57</t>
+          <t>13,94; 20,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,26; 24,64</t>
+          <t>16,59; 23,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,47; 21,2</t>
+          <t>15,25; 22,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,29; 21,4</t>
+          <t>12,6; 18,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,73; 20,31</t>
+          <t>17,21; 24,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,7; 23,78</t>
+          <t>17,48; 25,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,89; 22,21</t>
+          <t>14,54; 21,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,91; 19,42</t>
+          <t>13,95; 20,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,5; 21,27</t>
+          <t>16,25; 21,41</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,87; 22,91</t>
+          <t>17,69; 22,83</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,71; 20,56</t>
+          <t>15,68; 20,41</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,43; 19,27</t>
+          <t>14,17; 18,73</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7474</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4744</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10506</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7887</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>8732</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4778</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>3651</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6415</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>7474</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4744</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>10506</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8503</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14917</t>
+          <t>14370</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5180; 13533</t>
+          <t>3728; 12159</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1816; 9080</t>
+          <t>2060; 8714</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1335; 8363</t>
+          <t>6586; 15747</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3219; 12126</t>
+          <t>4014; 14118</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4047; 12255</t>
+          <t>5131; 14040</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2009; 8844</t>
+          <t>2083; 9632</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6337; 15483</t>
+          <t>1380; 7741</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4223; 14672</t>
+          <t>3194; 11280</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10857; 22398</t>
+          <t>10951; 22926</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5360; 15093</t>
+          <t>5382; 14943</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8454; 19918</t>
+          <t>9035; 21233</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9479; 22911</t>
+          <t>8651; 21009</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7428</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8037</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7229</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10354</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4695</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>10419</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>10726</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8408</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7428</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8037</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7229</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10874</t>
+          <t>8556</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19282</t>
+          <t>18910</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2095; 9192</t>
+          <t>4131; 12591</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6367; 15948</t>
+          <t>4391; 13506</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6400; 16090</t>
+          <t>3940; 12337</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4420; 14124</t>
+          <t>5958; 16165</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3922; 12339</t>
+          <t>1987; 8894</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4325; 12678</t>
+          <t>6337; 15677</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3550; 12730</t>
+          <t>6491; 16200</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6287; 17874</t>
+          <t>4627; 14801</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7668; 17712</t>
+          <t>7459; 17588</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12529; 25182</t>
+          <t>12469; 24666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12392; 24308</t>
+          <t>12418; 25168</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13019; 26867</t>
+          <t>13260; 26968</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>9194</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9719</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4143</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3441</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>7165</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>9258</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1958</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6249</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>9194</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>9719</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4143</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9897</t>
+          <t>9576</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3908; 11302</t>
+          <t>5026; 13835</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5418; 14588</t>
+          <t>5924; 14301</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>604; 5176</t>
+          <t>1496; 7797</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3234; 11074</t>
+          <t>1310; 7884</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5577; 14416</t>
+          <t>3928; 11677</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6122; 14979</t>
+          <t>5157; 14179</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1589; 7982</t>
+          <t>596; 5403</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1340; 7193</t>
+          <t>3088; 10572</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11155; 22486</t>
+          <t>11176; 22865</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13679; 25033</t>
+          <t>13348; 26024</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3186; 10791</t>
+          <t>2864; 10751</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5739; 15153</t>
+          <t>5734; 15551</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17067</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19781</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19636</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>31123</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>18585</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>22357</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>18826</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>23644</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>17067</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>19781</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>19636</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>33983</t>
+          <t>24415</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>57627</t>
+          <t>55538</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12865; 25544</t>
+          <t>11749; 23569</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16030; 29669</t>
+          <t>14148; 27032</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12884; 26568</t>
+          <t>12762; 26663</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17244; 32130</t>
+          <t>22653; 41654</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11259; 23207</t>
+          <t>12839; 25388</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14477; 27399</t>
+          <t>16096; 29553</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13880; 27687</t>
+          <t>13356; 25424</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25206; 43976</t>
+          <t>17247; 31845</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26752; 44613</t>
+          <t>27209; 44920</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33750; 52652</t>
+          <t>33569; 51873</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30137; 48335</t>
+          <t>29791; 49054</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45916; 70768</t>
+          <t>44890; 67624</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>14399</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>19509</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>15984</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>13605</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>16262</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>19295</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>17508</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>16413</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>14399</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>19509</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>15984</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15125</t>
+          <t>13683</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>31538</t>
+          <t>27288</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11130; 22035</t>
+          <t>9562; 20773</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13513; 25649</t>
+          <t>13346; 26298</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12323; 23671</t>
+          <t>10342; 22524</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10160; 25883</t>
+          <t>7297; 21378</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9486; 20506</t>
+          <t>11267; 21908</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13886; 26778</t>
+          <t>13241; 25632</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10965; 22426</t>
+          <t>11790; 23580</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8913; 24444</t>
+          <t>8480; 19857</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22807; 38183</t>
+          <t>23680; 38831</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30740; 49204</t>
+          <t>29920; 48861</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25628; 41810</t>
+          <t>26052; 42482</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>20962; 44718</t>
+          <t>19181; 37014</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2625</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6819</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7332</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3882</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>10661</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>3930</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>7714</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>6600</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2625</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>6819</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>7332</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>6835</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>10592</t>
+          <t>10718</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6832; 15553</t>
+          <t>665; 6459</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1369; 7409</t>
+          <t>3680; 10785</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4499; 12730</t>
+          <t>3886; 11611</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3629; 11659</t>
+          <t>705; 9148</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>659; 5953</t>
+          <t>6898; 15814</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3588; 11462</t>
+          <t>1788; 8008</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4014; 11878</t>
+          <t>4210; 12617</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1291; 9854</t>
+          <t>3634; 11320</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8394; 18561</t>
+          <t>8596; 19664</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6315; 15643</t>
+          <t>6331; 15946</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9707; 21527</t>
+          <t>10144; 21330</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6461; 18402</t>
+          <t>5946; 17797</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>95</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>58188</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>68610</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>64829</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>70292</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>66100</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>70037</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>60383</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>67729</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>58188</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>68610</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>64829</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>76125</t>
+          <t>66109</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>143853</t>
+          <t>136401</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>55151; 79388</t>
+          <t>47622; 71052</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>57972; 82771</t>
+          <t>56971; 81738</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>49603; 72667</t>
+          <t>53264; 77554</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>55259; 82782</t>
+          <t>57388; 85629</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>46922; 69388</t>
+          <t>55597; 80107</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>57373; 81694</t>
+          <t>58727; 84192</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>52010; 77573</t>
+          <t>49841; 73896</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>61784; 92942</t>
+          <t>54583; 79993</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>109721; 141389</t>
+          <t>108038; 142301</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>121408; 155692</t>
+          <t>120204; 155086</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>108738; 142245</t>
+          <t>108495; 141235</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>124867; 166820</t>
+          <t>120028; 158565</t>
         </is>
       </c>
     </row>
